--- a/sample-test-workbooks/EOA_NEOA_Sample_Test_Workbook.xlsx
+++ b/sample-test-workbooks/EOA_NEOA_Sample_Test_Workbook.xlsx
@@ -404,7 +404,7 @@
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="34.83203125" customWidth="1"/>
+    <col min="4" max="4" width="32.83203125" customWidth="1"/>
     <col min="5" max="5" width="27.83203125" customWidth="1"/>
     <col min="6" max="6" width="27.83203125" customWidth="1"/>
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
@@ -526,13 +526,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>EN60001</v>
+        <v>ENEO01</v>
       </c>
       <c r="C2" t="str">
-        <v>RF Site 08</v>
+        <v>RF Site 01</v>
       </c>
       <c r="D2" t="str">
-        <v>Sample Ivory Switching (EOA)</v>
+        <v>Sample Bravo Relay (EOA)</v>
       </c>
       <c r="E2" t="str">
         <v>IP Link Down</v>
@@ -615,13 +615,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>EN60002</v>
+        <v>ENEO02</v>
       </c>
       <c r="C3" t="str">
-        <v>RF Site 15</v>
+        <v>RF Site 02</v>
       </c>
       <c r="D3" t="str">
-        <v>Sample Palm Terminal (NEOA)</v>
+        <v>Sample Cedar Switching (EOA)</v>
       </c>
       <c r="E3" t="str">
         <v>Repeater</v>
@@ -633,7 +633,7 @@
         <v>Minor</v>
       </c>
       <c r="H3" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I3" t="str">
         <v>07/05/2026</v>
@@ -704,13 +704,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>EN60003</v>
+        <v>ENEO03</v>
       </c>
       <c r="C4" t="str">
-        <v>RF Site 22</v>
+        <v>RF Site 03</v>
       </c>
       <c r="D4" t="str">
-        <v>Sample Westbay Node (EOA)</v>
+        <v>Sample Delta Terminal (EOA)</v>
       </c>
       <c r="E4" t="str">
         <v>Router</v>
@@ -793,13 +793,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>EN60004</v>
+        <v>ENEO04</v>
       </c>
       <c r="C5" t="str">
-        <v>RF Site 29</v>
+        <v>RF Site 04</v>
       </c>
       <c r="D5" t="str">
-        <v>Sample Emerald Gateway (NEOA)</v>
+        <v>Sample Emerald Node (EOA)</v>
       </c>
       <c r="E5" t="str">
         <v>Switch</v>
@@ -811,7 +811,7 @@
         <v>Major</v>
       </c>
       <c r="H5" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I5" t="str">
         <v>13/05/2026</v>
@@ -882,13 +882,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>EN60005</v>
+        <v>ENEO05</v>
       </c>
       <c r="C6" t="str">
-        <v>RF Site 36</v>
+        <v>RF Site 05</v>
       </c>
       <c r="D6" t="str">
-        <v>Sample Lagoon Hub (EOA)</v>
+        <v>Sample Falcon Gateway (EOA)</v>
       </c>
       <c r="E6" t="str">
         <v>MW Link</v>
@@ -971,13 +971,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>EN60006</v>
+        <v>ENEO06</v>
       </c>
       <c r="C7" t="str">
-        <v>RF Site 43</v>
+        <v>RF Site 06</v>
       </c>
       <c r="D7" t="str">
-        <v>Sample Summit Relay (NEOA)</v>
+        <v>Sample Granite Hub (EOA)</v>
       </c>
       <c r="E7" t="str">
         <v>Power System</v>
@@ -989,7 +989,7 @@
         <v>Critical</v>
       </c>
       <c r="H7" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I7" t="str">
         <v>19/05/2026</v>
@@ -1060,13 +1060,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>EN60007</v>
+        <v>ENEO07</v>
       </c>
       <c r="C8" t="str">
-        <v>RF Site 50</v>
+        <v>RF Site 07</v>
       </c>
       <c r="D8" t="str">
-        <v>Sample Alpha Switching (EOA)</v>
+        <v>Sample Harbor Relay (EOA)</v>
       </c>
       <c r="E8" t="str">
         <v>Transmission Node</v>
@@ -1149,13 +1149,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>EN60008</v>
+        <v>ENEO08</v>
       </c>
       <c r="C9" t="str">
-        <v>RF Site 57</v>
+        <v>RF Site 08</v>
       </c>
       <c r="D9" t="str">
-        <v>Sample Harbor Terminal (NEOA)</v>
+        <v>Sample Ivory Switching (EOA)</v>
       </c>
       <c r="E9" t="str">
         <v>Access Node</v>
@@ -1167,7 +1167,7 @@
         <v>Minor</v>
       </c>
       <c r="H9" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I9" t="str">
         <v>25/05/2026</v>
@@ -1238,13 +1238,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>EN60009</v>
+        <v>ENEO09</v>
       </c>
       <c r="C10" t="str">
-        <v>RF Site 04</v>
+        <v>RF Site 09</v>
       </c>
       <c r="D10" t="str">
-        <v>Sample Emerald Node (EOA)</v>
+        <v>Sample Jasmine Terminal (EOA)</v>
       </c>
       <c r="E10" t="str">
         <v>Signal and Coverage issue</v>
@@ -1327,13 +1327,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>EN60010</v>
+        <v>ENEO10</v>
       </c>
       <c r="C11" t="str">
-        <v>RF Site 11</v>
+        <v>RF Site 10</v>
       </c>
       <c r="D11" t="str">
-        <v>Sample Lagoon Gateway (NEOA)</v>
+        <v>Sample Kingfisher Node (EOA)</v>
       </c>
       <c r="E11" t="str">
         <v>Complete site</v>
@@ -1345,7 +1345,7 @@
         <v>Major</v>
       </c>
       <c r="H11" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I11" t="str">
         <v>04/05/2026</v>
@@ -1416,13 +1416,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>EN60011</v>
+        <v>ENEO11</v>
       </c>
       <c r="C12" t="str">
-        <v>RF Site 18</v>
+        <v>RF Site 01</v>
       </c>
       <c r="D12" t="str">
-        <v>Sample Summit Hub (EOA)</v>
+        <v>Sample Bravo Relay (EOA)</v>
       </c>
       <c r="E12" t="str">
         <v>IP Link Down</v>
@@ -1505,13 +1505,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>EN60012</v>
+        <v>ENEO12</v>
       </c>
       <c r="C13" t="str">
-        <v>RF Site 25</v>
+        <v>RF Site 02</v>
       </c>
       <c r="D13" t="str">
-        <v>Sample Alpha Relay (NEOA)</v>
+        <v>Sample Cedar Switching (EOA)</v>
       </c>
       <c r="E13" t="str">
         <v>Repeater</v>
@@ -1523,7 +1523,7 @@
         <v>Critical</v>
       </c>
       <c r="H13" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I13" t="str">
         <v>10/05/2026</v>
@@ -1594,13 +1594,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>EN60013</v>
+        <v>ENEO13</v>
       </c>
       <c r="C14" t="str">
-        <v>RF Site 32</v>
+        <v>RF Site 03</v>
       </c>
       <c r="D14" t="str">
-        <v>Sample Harbor Switching (EOA)</v>
+        <v>Sample Delta Terminal (EOA)</v>
       </c>
       <c r="E14" t="str">
         <v>Router</v>
@@ -1683,13 +1683,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>EN60014</v>
+        <v>ENEO14</v>
       </c>
       <c r="C15" t="str">
-        <v>RF Site 39</v>
+        <v>RF Site 04</v>
       </c>
       <c r="D15" t="str">
-        <v>Sample Orchid Terminal (NEOA)</v>
+        <v>Sample Emerald Node (EOA)</v>
       </c>
       <c r="E15" t="str">
         <v>Switch</v>
@@ -1701,7 +1701,7 @@
         <v>Minor</v>
       </c>
       <c r="H15" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I15" t="str">
         <v>16/05/2026</v>
@@ -1772,13 +1772,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>EN60015</v>
+        <v>ENEO15</v>
       </c>
       <c r="C16" t="str">
-        <v>RF Site 46</v>
+        <v>RF Site 05</v>
       </c>
       <c r="D16" t="str">
-        <v>Sample Vertex Node (EOA)</v>
+        <v>Sample Falcon Gateway (EOA)</v>
       </c>
       <c r="E16" t="str">
         <v>MW Link</v>
@@ -1861,13 +1861,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>EN60016</v>
+        <v>ENEO16</v>
       </c>
       <c r="C17" t="str">
-        <v>RF Site 53</v>
+        <v>RF Site 06</v>
       </c>
       <c r="D17" t="str">
-        <v>Sample Delta Gateway (NEOA)</v>
+        <v>Sample Granite Hub (EOA)</v>
       </c>
       <c r="E17" t="str">
         <v>Power System</v>
@@ -1879,7 +1879,7 @@
         <v>Major</v>
       </c>
       <c r="H17" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I17" t="str">
         <v>22/05/2026</v>
@@ -1950,13 +1950,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>EN60017</v>
+        <v>ENEO17</v>
       </c>
       <c r="C18" t="str">
-        <v>RF Site 60</v>
+        <v>RF Site 07</v>
       </c>
       <c r="D18" t="str">
-        <v>Sample Kingfisher Hub (EOA)</v>
+        <v>Sample Harbor Relay (EOA)</v>
       </c>
       <c r="E18" t="str">
         <v>Transmission Node</v>
@@ -2039,13 +2039,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>EN60018</v>
+        <v>ENEO18</v>
       </c>
       <c r="C19" t="str">
-        <v>RF Site 07</v>
+        <v>RF Site 08</v>
       </c>
       <c r="D19" t="str">
-        <v>Sample Harbor Relay (NEOA)</v>
+        <v>Sample Ivory Switching (EOA)</v>
       </c>
       <c r="E19" t="str">
         <v>Access Node</v>
@@ -2057,7 +2057,7 @@
         <v>Critical</v>
       </c>
       <c r="H19" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I19" t="str">
         <v>01/05/2026</v>
@@ -2128,13 +2128,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>EN60019</v>
+        <v>ENEO19</v>
       </c>
       <c r="C20" t="str">
-        <v>RF Site 14</v>
+        <v>RF Site 09</v>
       </c>
       <c r="D20" t="str">
-        <v>Sample Orchid Switching (EOA)</v>
+        <v>Sample Jasmine Terminal (EOA)</v>
       </c>
       <c r="E20" t="str">
         <v>Signal and Coverage issue</v>
@@ -2217,13 +2217,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>EN60020</v>
+        <v>ENEO20</v>
       </c>
       <c r="C21" t="str">
-        <v>RF Site 21</v>
+        <v>RF Site 10</v>
       </c>
       <c r="D21" t="str">
-        <v>Sample Vertex Terminal (NEOA)</v>
+        <v>Sample Kingfisher Node (EOA)</v>
       </c>
       <c r="E21" t="str">
         <v>Complete site</v>
@@ -2235,7 +2235,7 @@
         <v>Minor</v>
       </c>
       <c r="H21" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I21" t="str">
         <v>07/05/2026</v>
@@ -2306,13 +2306,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>EN60021</v>
+        <v>ENEO21</v>
       </c>
       <c r="C22" t="str">
-        <v>RF Site 28</v>
+        <v>RF Site 01</v>
       </c>
       <c r="D22" t="str">
-        <v>Sample Delta Node (EOA)</v>
+        <v>Sample Bravo Relay (EOA)</v>
       </c>
       <c r="E22" t="str">
         <v>IP Link Down</v>
@@ -2395,13 +2395,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>EN60022</v>
+        <v>ENEO22</v>
       </c>
       <c r="C23" t="str">
-        <v>RF Site 35</v>
+        <v>RF Site 02</v>
       </c>
       <c r="D23" t="str">
-        <v>Sample Kingfisher Gateway (NEOA)</v>
+        <v>Sample Cedar Switching (EOA)</v>
       </c>
       <c r="E23" t="str">
         <v>Repeater</v>
@@ -2413,7 +2413,7 @@
         <v>Major</v>
       </c>
       <c r="H23" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I23" t="str">
         <v>13/05/2026</v>
@@ -2484,13 +2484,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>EN60023</v>
+        <v>ENEO23</v>
       </c>
       <c r="C24" t="str">
-        <v>RF Site 42</v>
+        <v>RF Site 03</v>
       </c>
       <c r="D24" t="str">
-        <v>Sample River Hub (EOA)</v>
+        <v>Sample Delta Terminal (EOA)</v>
       </c>
       <c r="E24" t="str">
         <v>Router</v>
@@ -2573,13 +2573,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>EN60024</v>
+        <v>ENEO24</v>
       </c>
       <c r="C25" t="str">
-        <v>RF Site 49</v>
+        <v>RF Site 04</v>
       </c>
       <c r="D25" t="str">
-        <v>Sample Zenith Relay (NEOA)</v>
+        <v>Sample Emerald Node (EOA)</v>
       </c>
       <c r="E25" t="str">
         <v>Switch</v>
@@ -2591,7 +2591,7 @@
         <v>Critical</v>
       </c>
       <c r="H25" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I25" t="str">
         <v>19/05/2026</v>
@@ -2662,13 +2662,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>EN60025</v>
+        <v>ENEO25</v>
       </c>
       <c r="C26" t="str">
-        <v>RF Site 56</v>
+        <v>RF Site 05</v>
       </c>
       <c r="D26" t="str">
-        <v>Sample Granite Switching (EOA)</v>
+        <v>Sample Falcon Gateway (EOA)</v>
       </c>
       <c r="E26" t="str">
         <v>MW Link</v>
@@ -2751,13 +2751,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>EN60026</v>
+        <v>ENEO26</v>
       </c>
       <c r="C27" t="str">
-        <v>RF Site 03</v>
+        <v>RF Site 06</v>
       </c>
       <c r="D27" t="str">
-        <v>Sample Delta Terminal (NEOA)</v>
+        <v>Sample Granite Hub (EOA)</v>
       </c>
       <c r="E27" t="str">
         <v>Power System</v>
@@ -2769,7 +2769,7 @@
         <v>Minor</v>
       </c>
       <c r="H27" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I27" t="str">
         <v>25/05/2026</v>
@@ -2840,13 +2840,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>EN60027</v>
+        <v>ENEO27</v>
       </c>
       <c r="C28" t="str">
-        <v>RF Site 10</v>
+        <v>RF Site 07</v>
       </c>
       <c r="D28" t="str">
-        <v>Sample Kingfisher Node (EOA)</v>
+        <v>Sample Harbor Relay (EOA)</v>
       </c>
       <c r="E28" t="str">
         <v>Transmission Node</v>
@@ -2929,13 +2929,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>EN60028</v>
+        <v>ENEO28</v>
       </c>
       <c r="C29" t="str">
-        <v>RF Site 17</v>
+        <v>RF Site 08</v>
       </c>
       <c r="D29" t="str">
-        <v>Sample River Gateway (NEOA)</v>
+        <v>Sample Ivory Switching (EOA)</v>
       </c>
       <c r="E29" t="str">
         <v>Access Node</v>
@@ -2947,7 +2947,7 @@
         <v>Major</v>
       </c>
       <c r="H29" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I29" t="str">
         <v>04/05/2026</v>
@@ -3018,13 +3018,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>EN60029</v>
+        <v>ENEO29</v>
       </c>
       <c r="C30" t="str">
-        <v>RF Site 24</v>
+        <v>RF Site 09</v>
       </c>
       <c r="D30" t="str">
-        <v>Sample Zenith Hub (EOA)</v>
+        <v>Sample Jasmine Terminal (EOA)</v>
       </c>
       <c r="E30" t="str">
         <v>Signal and Coverage issue</v>
@@ -3107,13 +3107,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>EN60030</v>
+        <v>ENEO30</v>
       </c>
       <c r="C31" t="str">
-        <v>RF Site 31</v>
+        <v>RF Site 10</v>
       </c>
       <c r="D31" t="str">
-        <v>Sample Granite Relay (NEOA)</v>
+        <v>Sample Kingfisher Node (EOA)</v>
       </c>
       <c r="E31" t="str">
         <v>Complete site</v>
@@ -3125,7 +3125,7 @@
         <v>Critical</v>
       </c>
       <c r="H31" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I31" t="str">
         <v>10/05/2026</v>
@@ -3196,13 +3196,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>EN60031</v>
+        <v>ENEO31</v>
       </c>
       <c r="C32" t="str">
-        <v>RF Site 38</v>
+        <v>RF Site 01</v>
       </c>
       <c r="D32" t="str">
-        <v>Sample Northstar Switching (EOA)</v>
+        <v>Sample Bravo Relay (EOA)</v>
       </c>
       <c r="E32" t="str">
         <v>IP Link Down</v>
@@ -3285,13 +3285,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>EN60032</v>
+        <v>ENEO32</v>
       </c>
       <c r="C33" t="str">
-        <v>RF Site 45</v>
+        <v>RF Site 02</v>
       </c>
       <c r="D33" t="str">
-        <v>Sample Unity Terminal (NEOA)</v>
+        <v>Sample Cedar Switching (EOA)</v>
       </c>
       <c r="E33" t="str">
         <v>Repeater</v>
@@ -3303,7 +3303,7 @@
         <v>Minor</v>
       </c>
       <c r="H33" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I33" t="str">
         <v>16/05/2026</v>
@@ -3374,13 +3374,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>EN60033</v>
+        <v>ENEO33</v>
       </c>
       <c r="C34" t="str">
-        <v>RF Site 52</v>
+        <v>RF Site 03</v>
       </c>
       <c r="D34" t="str">
-        <v>Sample Cedar Node (EOA)</v>
+        <v>Sample Delta Terminal (EOA)</v>
       </c>
       <c r="E34" t="str">
         <v>Router</v>
@@ -3463,13 +3463,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>EN60034</v>
+        <v>ENEO34</v>
       </c>
       <c r="C35" t="str">
-        <v>RF Site 59</v>
+        <v>RF Site 04</v>
       </c>
       <c r="D35" t="str">
-        <v>Sample Jasmine Gateway (NEOA)</v>
+        <v>Sample Emerald Node (EOA)</v>
       </c>
       <c r="E35" t="str">
         <v>Switch</v>
@@ -3481,7 +3481,7 @@
         <v>Major</v>
       </c>
       <c r="H35" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I35" t="str">
         <v>22/05/2026</v>
@@ -3552,13 +3552,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>EN60035</v>
+        <v>ENEO35</v>
       </c>
       <c r="C36" t="str">
-        <v>RF Site 06</v>
+        <v>RF Site 05</v>
       </c>
       <c r="D36" t="str">
-        <v>Sample Granite Hub (EOA)</v>
+        <v>Sample Falcon Gateway (EOA)</v>
       </c>
       <c r="E36" t="str">
         <v>MW Link</v>
@@ -3641,13 +3641,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>EN60036</v>
+        <v>ENEO36</v>
       </c>
       <c r="C37" t="str">
-        <v>RF Site 13</v>
+        <v>RF Site 06</v>
       </c>
       <c r="D37" t="str">
-        <v>Sample Northstar Relay (NEOA)</v>
+        <v>Sample Granite Hub (EOA)</v>
       </c>
       <c r="E37" t="str">
         <v>Power System</v>
@@ -3659,7 +3659,7 @@
         <v>Critical</v>
       </c>
       <c r="H37" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I37" t="str">
         <v>01/05/2026</v>
@@ -3730,13 +3730,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>EN60037</v>
+        <v>ENEO37</v>
       </c>
       <c r="C38" t="str">
-        <v>RF Site 20</v>
+        <v>RF Site 07</v>
       </c>
       <c r="D38" t="str">
-        <v>Sample Unity Switching (EOA)</v>
+        <v>Sample Harbor Relay (EOA)</v>
       </c>
       <c r="E38" t="str">
         <v>Transmission Node</v>
@@ -3819,13 +3819,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>EN60038</v>
+        <v>ENEO38</v>
       </c>
       <c r="C39" t="str">
-        <v>RF Site 27</v>
+        <v>RF Site 08</v>
       </c>
       <c r="D39" t="str">
-        <v>Sample Cedar Terminal (NEOA)</v>
+        <v>Sample Ivory Switching (EOA)</v>
       </c>
       <c r="E39" t="str">
         <v>Access Node</v>
@@ -3837,7 +3837,7 @@
         <v>Minor</v>
       </c>
       <c r="H39" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I39" t="str">
         <v>07/05/2026</v>
@@ -3908,13 +3908,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>EN60039</v>
+        <v>ENEO39</v>
       </c>
       <c r="C40" t="str">
-        <v>RF Site 34</v>
+        <v>RF Site 09</v>
       </c>
       <c r="D40" t="str">
-        <v>Sample Jasmine Node (EOA)</v>
+        <v>Sample Jasmine Terminal (EOA)</v>
       </c>
       <c r="E40" t="str">
         <v>Signal and Coverage issue</v>
@@ -3997,13 +3997,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>EN60040</v>
+        <v>ENEO40</v>
       </c>
       <c r="C41" t="str">
-        <v>RF Site 41</v>
+        <v>RF Site 10</v>
       </c>
       <c r="D41" t="str">
-        <v>Sample Quartz Gateway (NEOA)</v>
+        <v>Sample Kingfisher Node (EOA)</v>
       </c>
       <c r="E41" t="str">
         <v>Complete site</v>
@@ -4015,7 +4015,7 @@
         <v>Major</v>
       </c>
       <c r="H41" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I41" t="str">
         <v>13/05/2026</v>
@@ -4086,13 +4086,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>EN60041</v>
+        <v>ENEO41</v>
       </c>
       <c r="C42" t="str">
-        <v>RF Site 48</v>
+        <v>RF Site 01</v>
       </c>
       <c r="D42" t="str">
-        <v>Sample Yard Hub (EOA)</v>
+        <v>Sample Bravo Relay (EOA)</v>
       </c>
       <c r="E42" t="str">
         <v>IP Link Down</v>
@@ -4175,13 +4175,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>EN60042</v>
+        <v>ENEO42</v>
       </c>
       <c r="C43" t="str">
-        <v>RF Site 55</v>
+        <v>RF Site 02</v>
       </c>
       <c r="D43" t="str">
-        <v>Sample Falcon Relay (NEOA)</v>
+        <v>Sample Cedar Switching (EOA)</v>
       </c>
       <c r="E43" t="str">
         <v>Repeater</v>
@@ -4193,7 +4193,7 @@
         <v>Critical</v>
       </c>
       <c r="H43" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I43" t="str">
         <v>19/05/2026</v>
@@ -4264,13 +4264,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>EN60043</v>
+        <v>ENEO43</v>
       </c>
       <c r="C44" t="str">
-        <v>RF Site 02</v>
+        <v>RF Site 03</v>
       </c>
       <c r="D44" t="str">
-        <v>Sample Cedar Switching (EOA)</v>
+        <v>Sample Delta Terminal (EOA)</v>
       </c>
       <c r="E44" t="str">
         <v>Router</v>
@@ -4353,13 +4353,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>EN60044</v>
+        <v>ENEO44</v>
       </c>
       <c r="C45" t="str">
-        <v>RF Site 09</v>
+        <v>RF Site 04</v>
       </c>
       <c r="D45" t="str">
-        <v>Sample Jasmine Terminal (NEOA)</v>
+        <v>Sample Emerald Node (EOA)</v>
       </c>
       <c r="E45" t="str">
         <v>Switch</v>
@@ -4371,7 +4371,7 @@
         <v>Minor</v>
       </c>
       <c r="H45" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I45" t="str">
         <v>25/05/2026</v>
@@ -4442,13 +4442,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>EN60045</v>
+        <v>ENEO45</v>
       </c>
       <c r="C46" t="str">
-        <v>RF Site 16</v>
+        <v>RF Site 05</v>
       </c>
       <c r="D46" t="str">
-        <v>Sample Quartz Node (EOA)</v>
+        <v>Sample Falcon Gateway (EOA)</v>
       </c>
       <c r="E46" t="str">
         <v>MW Link</v>
@@ -4531,13 +4531,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>EN60046</v>
+        <v>ENEO46</v>
       </c>
       <c r="C47" t="str">
-        <v>RF Site 23</v>
+        <v>RF Site 06</v>
       </c>
       <c r="D47" t="str">
-        <v>Sample Yard Gateway (NEOA)</v>
+        <v>Sample Granite Hub (EOA)</v>
       </c>
       <c r="E47" t="str">
         <v>Power System</v>
@@ -4549,7 +4549,7 @@
         <v>Major</v>
       </c>
       <c r="H47" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I47" t="str">
         <v>04/05/2026</v>
@@ -4620,13 +4620,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>EN60047</v>
+        <v>ENEO47</v>
       </c>
       <c r="C48" t="str">
-        <v>RF Site 30</v>
+        <v>RF Site 07</v>
       </c>
       <c r="D48" t="str">
-        <v>Sample Falcon Hub (EOA)</v>
+        <v>Sample Harbor Relay (EOA)</v>
       </c>
       <c r="E48" t="str">
         <v>Transmission Node</v>
@@ -4709,13 +4709,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>EN60048</v>
+        <v>ENEO48</v>
       </c>
       <c r="C49" t="str">
-        <v>RF Site 37</v>
+        <v>RF Site 08</v>
       </c>
       <c r="D49" t="str">
-        <v>Sample Metro Relay (NEOA)</v>
+        <v>Sample Ivory Switching (EOA)</v>
       </c>
       <c r="E49" t="str">
         <v>Access Node</v>
@@ -4727,7 +4727,7 @@
         <v>Critical</v>
       </c>
       <c r="H49" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I49" t="str">
         <v>10/05/2026</v>
@@ -4798,13 +4798,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>EN60049</v>
+        <v>ENEO49</v>
       </c>
       <c r="C50" t="str">
-        <v>RF Site 44</v>
+        <v>RF Site 09</v>
       </c>
       <c r="D50" t="str">
-        <v>Sample Tide Switching (EOA)</v>
+        <v>Sample Jasmine Terminal (EOA)</v>
       </c>
       <c r="E50" t="str">
         <v>Signal and Coverage issue</v>
@@ -4887,13 +4887,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>EN60050</v>
+        <v>ENEO50</v>
       </c>
       <c r="C51" t="str">
-        <v>RF Site 51</v>
+        <v>RF Site 10</v>
       </c>
       <c r="D51" t="str">
-        <v>Sample Bravo Terminal (NEOA)</v>
+        <v>Sample Kingfisher Node (EOA)</v>
       </c>
       <c r="E51" t="str">
         <v>Complete site</v>
@@ -4905,7 +4905,7 @@
         <v>Minor</v>
       </c>
       <c r="H51" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
       <c r="I51" t="str">
         <v>16/05/2026</v>
@@ -4976,13 +4976,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>EN60051</v>
+        <v>ENNE01</v>
       </c>
       <c r="C52" t="str">
-        <v>RF Site 58</v>
+        <v>RF Site 11</v>
       </c>
       <c r="D52" t="str">
-        <v>Sample Ivory Node (EOA)</v>
+        <v>Sample Lagoon Gateway (NEOA)</v>
       </c>
       <c r="E52" t="str">
         <v>IP Link Down</v>
@@ -4994,7 +4994,7 @@
         <v>Critical</v>
       </c>
       <c r="H52" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I52" t="str">
         <v>19/05/2026</v>
@@ -5065,13 +5065,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>EN60052</v>
+        <v>ENNE02</v>
       </c>
       <c r="C53" t="str">
-        <v>RF Site 05</v>
+        <v>RF Site 12</v>
       </c>
       <c r="D53" t="str">
-        <v>Sample Falcon Gateway (NEOA)</v>
+        <v>Sample Metro Hub (NEOA)</v>
       </c>
       <c r="E53" t="str">
         <v>Repeater</v>
@@ -5154,13 +5154,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>EN60053</v>
+        <v>ENNE03</v>
       </c>
       <c r="C54" t="str">
-        <v>RF Site 12</v>
+        <v>RF Site 13</v>
       </c>
       <c r="D54" t="str">
-        <v>Sample Metro Hub (EOA)</v>
+        <v>Sample Northstar Relay (NEOA)</v>
       </c>
       <c r="E54" t="str">
         <v>Router</v>
@@ -5172,7 +5172,7 @@
         <v>Minor</v>
       </c>
       <c r="H54" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I54" t="str">
         <v>25/05/2026</v>
@@ -5243,13 +5243,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>EN60054</v>
+        <v>ENNE04</v>
       </c>
       <c r="C55" t="str">
-        <v>RF Site 19</v>
+        <v>RF Site 14</v>
       </c>
       <c r="D55" t="str">
-        <v>Sample Tide Relay (NEOA)</v>
+        <v>Sample Orchid Switching (NEOA)</v>
       </c>
       <c r="E55" t="str">
         <v>Switch</v>
@@ -5332,13 +5332,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>EN60055</v>
+        <v>ENNE05</v>
       </c>
       <c r="C56" t="str">
-        <v>RF Site 26</v>
+        <v>RF Site 15</v>
       </c>
       <c r="D56" t="str">
-        <v>Sample Bravo Switching (EOA)</v>
+        <v>Sample Palm Terminal (NEOA)</v>
       </c>
       <c r="E56" t="str">
         <v>MW Link</v>
@@ -5350,7 +5350,7 @@
         <v>Major</v>
       </c>
       <c r="H56" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I56" t="str">
         <v>04/05/2026</v>
@@ -5421,13 +5421,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>EN60056</v>
+        <v>ENNE06</v>
       </c>
       <c r="C57" t="str">
-        <v>RF Site 33</v>
+        <v>RF Site 16</v>
       </c>
       <c r="D57" t="str">
-        <v>Sample Ivory Terminal (NEOA)</v>
+        <v>Sample Quartz Node (NEOA)</v>
       </c>
       <c r="E57" t="str">
         <v>Power System</v>
@@ -5510,13 +5510,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>EN60057</v>
+        <v>ENNE07</v>
       </c>
       <c r="C58" t="str">
-        <v>RF Site 40</v>
+        <v>RF Site 17</v>
       </c>
       <c r="D58" t="str">
-        <v>Sample Palm Node (EOA)</v>
+        <v>Sample River Gateway (NEOA)</v>
       </c>
       <c r="E58" t="str">
         <v>Transmission Node</v>
@@ -5528,7 +5528,7 @@
         <v>Critical</v>
       </c>
       <c r="H58" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I58" t="str">
         <v>10/05/2026</v>
@@ -5599,13 +5599,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>EN60058</v>
+        <v>ENNE08</v>
       </c>
       <c r="C59" t="str">
-        <v>RF Site 47</v>
+        <v>RF Site 18</v>
       </c>
       <c r="D59" t="str">
-        <v>Sample Westbay Gateway (NEOA)</v>
+        <v>Sample Summit Hub (NEOA)</v>
       </c>
       <c r="E59" t="str">
         <v>Access Node</v>
@@ -5688,13 +5688,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>EN60059</v>
+        <v>ENNE09</v>
       </c>
       <c r="C60" t="str">
-        <v>RF Site 54</v>
+        <v>RF Site 19</v>
       </c>
       <c r="D60" t="str">
-        <v>Sample Emerald Hub (EOA)</v>
+        <v>Sample Tide Relay (NEOA)</v>
       </c>
       <c r="E60" t="str">
         <v>Signal and Coverage issue</v>
@@ -5706,7 +5706,7 @@
         <v>Minor</v>
       </c>
       <c r="H60" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I60" t="str">
         <v>16/05/2026</v>
@@ -5777,13 +5777,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>EN60060</v>
+        <v>ENNE10</v>
       </c>
       <c r="C61" t="str">
-        <v>RF Site 01</v>
+        <v>RF Site 20</v>
       </c>
       <c r="D61" t="str">
-        <v>Sample Bravo Relay (NEOA)</v>
+        <v>Sample Unity Switching (NEOA)</v>
       </c>
       <c r="E61" t="str">
         <v>Complete site</v>
@@ -5866,13 +5866,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>EN60061</v>
+        <v>ENNE11</v>
       </c>
       <c r="C62" t="str">
-        <v>RF Site 08</v>
+        <v>RF Site 11</v>
       </c>
       <c r="D62" t="str">
-        <v>Sample Ivory Switching (EOA)</v>
+        <v>Sample Lagoon Gateway (NEOA)</v>
       </c>
       <c r="E62" t="str">
         <v>IP Link Down</v>
@@ -5884,7 +5884,7 @@
         <v>Major</v>
       </c>
       <c r="H62" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I62" t="str">
         <v>22/05/2026</v>
@@ -5955,13 +5955,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>EN60062</v>
+        <v>ENNE12</v>
       </c>
       <c r="C63" t="str">
-        <v>RF Site 15</v>
+        <v>RF Site 12</v>
       </c>
       <c r="D63" t="str">
-        <v>Sample Palm Terminal (NEOA)</v>
+        <v>Sample Metro Hub (NEOA)</v>
       </c>
       <c r="E63" t="str">
         <v>Repeater</v>
@@ -6044,13 +6044,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>EN60063</v>
+        <v>ENNE13</v>
       </c>
       <c r="C64" t="str">
-        <v>RF Site 22</v>
+        <v>RF Site 13</v>
       </c>
       <c r="D64" t="str">
-        <v>Sample Westbay Node (EOA)</v>
+        <v>Sample Northstar Relay (NEOA)</v>
       </c>
       <c r="E64" t="str">
         <v>Router</v>
@@ -6062,7 +6062,7 @@
         <v>Critical</v>
       </c>
       <c r="H64" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I64" t="str">
         <v>01/05/2026</v>
@@ -6133,13 +6133,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>EN60064</v>
+        <v>ENNE14</v>
       </c>
       <c r="C65" t="str">
-        <v>RF Site 29</v>
+        <v>RF Site 14</v>
       </c>
       <c r="D65" t="str">
-        <v>Sample Emerald Gateway (NEOA)</v>
+        <v>Sample Orchid Switching (NEOA)</v>
       </c>
       <c r="E65" t="str">
         <v>Switch</v>
@@ -6222,13 +6222,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>EN60065</v>
+        <v>ENNE15</v>
       </c>
       <c r="C66" t="str">
-        <v>RF Site 36</v>
+        <v>RF Site 15</v>
       </c>
       <c r="D66" t="str">
-        <v>Sample Lagoon Hub (EOA)</v>
+        <v>Sample Palm Terminal (NEOA)</v>
       </c>
       <c r="E66" t="str">
         <v>MW Link</v>
@@ -6240,7 +6240,7 @@
         <v>Minor</v>
       </c>
       <c r="H66" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I66" t="str">
         <v>07/05/2026</v>
@@ -6311,13 +6311,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>EN60066</v>
+        <v>ENNE16</v>
       </c>
       <c r="C67" t="str">
-        <v>RF Site 43</v>
+        <v>RF Site 16</v>
       </c>
       <c r="D67" t="str">
-        <v>Sample Summit Relay (NEOA)</v>
+        <v>Sample Quartz Node (NEOA)</v>
       </c>
       <c r="E67" t="str">
         <v>Power System</v>
@@ -6400,13 +6400,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>EN60067</v>
+        <v>ENNE17</v>
       </c>
       <c r="C68" t="str">
-        <v>RF Site 50</v>
+        <v>RF Site 17</v>
       </c>
       <c r="D68" t="str">
-        <v>Sample Alpha Switching (EOA)</v>
+        <v>Sample River Gateway (NEOA)</v>
       </c>
       <c r="E68" t="str">
         <v>Transmission Node</v>
@@ -6418,7 +6418,7 @@
         <v>Major</v>
       </c>
       <c r="H68" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I68" t="str">
         <v>13/05/2026</v>
@@ -6489,13 +6489,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>EN60068</v>
+        <v>ENNE18</v>
       </c>
       <c r="C69" t="str">
-        <v>RF Site 57</v>
+        <v>RF Site 18</v>
       </c>
       <c r="D69" t="str">
-        <v>Sample Harbor Terminal (NEOA)</v>
+        <v>Sample Summit Hub (NEOA)</v>
       </c>
       <c r="E69" t="str">
         <v>Access Node</v>
@@ -6578,13 +6578,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>EN60069</v>
+        <v>ENNE19</v>
       </c>
       <c r="C70" t="str">
-        <v>RF Site 04</v>
+        <v>RF Site 19</v>
       </c>
       <c r="D70" t="str">
-        <v>Sample Emerald Node (EOA)</v>
+        <v>Sample Tide Relay (NEOA)</v>
       </c>
       <c r="E70" t="str">
         <v>Signal and Coverage issue</v>
@@ -6596,7 +6596,7 @@
         <v>Critical</v>
       </c>
       <c r="H70" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I70" t="str">
         <v>19/05/2026</v>
@@ -6667,13 +6667,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>EN60070</v>
+        <v>ENNE20</v>
       </c>
       <c r="C71" t="str">
-        <v>RF Site 11</v>
+        <v>RF Site 20</v>
       </c>
       <c r="D71" t="str">
-        <v>Sample Lagoon Gateway (NEOA)</v>
+        <v>Sample Unity Switching (NEOA)</v>
       </c>
       <c r="E71" t="str">
         <v>Complete site</v>
@@ -6756,13 +6756,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>EN60071</v>
+        <v>ENNE21</v>
       </c>
       <c r="C72" t="str">
-        <v>RF Site 18</v>
+        <v>RF Site 11</v>
       </c>
       <c r="D72" t="str">
-        <v>Sample Summit Hub (EOA)</v>
+        <v>Sample Lagoon Gateway (NEOA)</v>
       </c>
       <c r="E72" t="str">
         <v>IP Link Down</v>
@@ -6774,7 +6774,7 @@
         <v>Minor</v>
       </c>
       <c r="H72" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I72" t="str">
         <v>25/05/2026</v>
@@ -6845,13 +6845,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>EN60072</v>
+        <v>ENNE22</v>
       </c>
       <c r="C73" t="str">
-        <v>RF Site 25</v>
+        <v>RF Site 12</v>
       </c>
       <c r="D73" t="str">
-        <v>Sample Alpha Relay (NEOA)</v>
+        <v>Sample Metro Hub (NEOA)</v>
       </c>
       <c r="E73" t="str">
         <v>Repeater</v>
@@ -6934,13 +6934,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>EN60073</v>
+        <v>ENNE23</v>
       </c>
       <c r="C74" t="str">
-        <v>RF Site 32</v>
+        <v>RF Site 13</v>
       </c>
       <c r="D74" t="str">
-        <v>Sample Harbor Switching (EOA)</v>
+        <v>Sample Northstar Relay (NEOA)</v>
       </c>
       <c r="E74" t="str">
         <v>Router</v>
@@ -6952,7 +6952,7 @@
         <v>Major</v>
       </c>
       <c r="H74" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I74" t="str">
         <v>04/05/2026</v>
@@ -7023,13 +7023,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>EN60074</v>
+        <v>ENNE24</v>
       </c>
       <c r="C75" t="str">
-        <v>RF Site 39</v>
+        <v>RF Site 14</v>
       </c>
       <c r="D75" t="str">
-        <v>Sample Orchid Terminal (NEOA)</v>
+        <v>Sample Orchid Switching (NEOA)</v>
       </c>
       <c r="E75" t="str">
         <v>Switch</v>
@@ -7112,13 +7112,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>EN60075</v>
+        <v>ENNE25</v>
       </c>
       <c r="C76" t="str">
-        <v>RF Site 46</v>
+        <v>RF Site 15</v>
       </c>
       <c r="D76" t="str">
-        <v>Sample Vertex Node (EOA)</v>
+        <v>Sample Palm Terminal (NEOA)</v>
       </c>
       <c r="E76" t="str">
         <v>MW Link</v>
@@ -7130,7 +7130,7 @@
         <v>Critical</v>
       </c>
       <c r="H76" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I76" t="str">
         <v>10/05/2026</v>
@@ -7201,13 +7201,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>EN60076</v>
+        <v>ENNE26</v>
       </c>
       <c r="C77" t="str">
-        <v>RF Site 53</v>
+        <v>RF Site 16</v>
       </c>
       <c r="D77" t="str">
-        <v>Sample Delta Gateway (NEOA)</v>
+        <v>Sample Quartz Node (NEOA)</v>
       </c>
       <c r="E77" t="str">
         <v>Power System</v>
@@ -7290,13 +7290,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>EN60077</v>
+        <v>ENNE27</v>
       </c>
       <c r="C78" t="str">
-        <v>RF Site 60</v>
+        <v>RF Site 17</v>
       </c>
       <c r="D78" t="str">
-        <v>Sample Kingfisher Hub (EOA)</v>
+        <v>Sample River Gateway (NEOA)</v>
       </c>
       <c r="E78" t="str">
         <v>Transmission Node</v>
@@ -7308,7 +7308,7 @@
         <v>Minor</v>
       </c>
       <c r="H78" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I78" t="str">
         <v>16/05/2026</v>
@@ -7379,13 +7379,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>EN60078</v>
+        <v>ENNE28</v>
       </c>
       <c r="C79" t="str">
-        <v>RF Site 07</v>
+        <v>RF Site 18</v>
       </c>
       <c r="D79" t="str">
-        <v>Sample Harbor Relay (NEOA)</v>
+        <v>Sample Summit Hub (NEOA)</v>
       </c>
       <c r="E79" t="str">
         <v>Access Node</v>
@@ -7468,13 +7468,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>EN60079</v>
+        <v>ENNE29</v>
       </c>
       <c r="C80" t="str">
-        <v>RF Site 14</v>
+        <v>RF Site 19</v>
       </c>
       <c r="D80" t="str">
-        <v>Sample Orchid Switching (EOA)</v>
+        <v>Sample Tide Relay (NEOA)</v>
       </c>
       <c r="E80" t="str">
         <v>Signal and Coverage issue</v>
@@ -7486,7 +7486,7 @@
         <v>Major</v>
       </c>
       <c r="H80" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I80" t="str">
         <v>22/05/2026</v>
@@ -7557,13 +7557,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="str">
-        <v>EN60080</v>
+        <v>ENNE30</v>
       </c>
       <c r="C81" t="str">
-        <v>RF Site 21</v>
+        <v>RF Site 20</v>
       </c>
       <c r="D81" t="str">
-        <v>Sample Vertex Terminal (NEOA)</v>
+        <v>Sample Unity Switching (NEOA)</v>
       </c>
       <c r="E81" t="str">
         <v>Complete site</v>
@@ -7646,13 +7646,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="str">
-        <v>EN60081</v>
+        <v>ENNE31</v>
       </c>
       <c r="C82" t="str">
-        <v>RF Site 28</v>
+        <v>RF Site 11</v>
       </c>
       <c r="D82" t="str">
-        <v>Sample Delta Node (EOA)</v>
+        <v>Sample Lagoon Gateway (NEOA)</v>
       </c>
       <c r="E82" t="str">
         <v>IP Link Down</v>
@@ -7664,7 +7664,7 @@
         <v>Critical</v>
       </c>
       <c r="H82" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I82" t="str">
         <v>01/05/2026</v>
@@ -7735,13 +7735,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="str">
-        <v>EN60082</v>
+        <v>ENNE32</v>
       </c>
       <c r="C83" t="str">
-        <v>RF Site 35</v>
+        <v>RF Site 12</v>
       </c>
       <c r="D83" t="str">
-        <v>Sample Kingfisher Gateway (NEOA)</v>
+        <v>Sample Metro Hub (NEOA)</v>
       </c>
       <c r="E83" t="str">
         <v>Repeater</v>
@@ -7824,13 +7824,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="str">
-        <v>EN60083</v>
+        <v>ENNE33</v>
       </c>
       <c r="C84" t="str">
-        <v>RF Site 42</v>
+        <v>RF Site 13</v>
       </c>
       <c r="D84" t="str">
-        <v>Sample River Hub (EOA)</v>
+        <v>Sample Northstar Relay (NEOA)</v>
       </c>
       <c r="E84" t="str">
         <v>Router</v>
@@ -7842,7 +7842,7 @@
         <v>Minor</v>
       </c>
       <c r="H84" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I84" t="str">
         <v>07/05/2026</v>
@@ -7913,13 +7913,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>EN60084</v>
+        <v>ENNE34</v>
       </c>
       <c r="C85" t="str">
-        <v>RF Site 49</v>
+        <v>RF Site 14</v>
       </c>
       <c r="D85" t="str">
-        <v>Sample Zenith Relay (NEOA)</v>
+        <v>Sample Orchid Switching (NEOA)</v>
       </c>
       <c r="E85" t="str">
         <v>Switch</v>
@@ -8002,13 +8002,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>EN60085</v>
+        <v>ENNE35</v>
       </c>
       <c r="C86" t="str">
-        <v>RF Site 56</v>
+        <v>RF Site 15</v>
       </c>
       <c r="D86" t="str">
-        <v>Sample Granite Switching (EOA)</v>
+        <v>Sample Palm Terminal (NEOA)</v>
       </c>
       <c r="E86" t="str">
         <v>MW Link</v>
@@ -8020,7 +8020,7 @@
         <v>Major</v>
       </c>
       <c r="H86" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I86" t="str">
         <v>13/05/2026</v>
@@ -8091,13 +8091,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>EN60086</v>
+        <v>ENNE36</v>
       </c>
       <c r="C87" t="str">
-        <v>RF Site 03</v>
+        <v>RF Site 16</v>
       </c>
       <c r="D87" t="str">
-        <v>Sample Delta Terminal (NEOA)</v>
+        <v>Sample Quartz Node (NEOA)</v>
       </c>
       <c r="E87" t="str">
         <v>Power System</v>
@@ -8180,13 +8180,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>EN60087</v>
+        <v>ENNE37</v>
       </c>
       <c r="C88" t="str">
-        <v>RF Site 10</v>
+        <v>RF Site 17</v>
       </c>
       <c r="D88" t="str">
-        <v>Sample Kingfisher Node (EOA)</v>
+        <v>Sample River Gateway (NEOA)</v>
       </c>
       <c r="E88" t="str">
         <v>Transmission Node</v>
@@ -8198,7 +8198,7 @@
         <v>Critical</v>
       </c>
       <c r="H88" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I88" t="str">
         <v>19/05/2026</v>
@@ -8269,13 +8269,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="str">
-        <v>EN60088</v>
+        <v>ENNE38</v>
       </c>
       <c r="C89" t="str">
-        <v>RF Site 17</v>
+        <v>RF Site 18</v>
       </c>
       <c r="D89" t="str">
-        <v>Sample River Gateway (NEOA)</v>
+        <v>Sample Summit Hub (NEOA)</v>
       </c>
       <c r="E89" t="str">
         <v>Access Node</v>
@@ -8358,13 +8358,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="str">
-        <v>EN60089</v>
+        <v>ENNE39</v>
       </c>
       <c r="C90" t="str">
-        <v>RF Site 24</v>
+        <v>RF Site 19</v>
       </c>
       <c r="D90" t="str">
-        <v>Sample Zenith Hub (EOA)</v>
+        <v>Sample Tide Relay (NEOA)</v>
       </c>
       <c r="E90" t="str">
         <v>Signal and Coverage issue</v>
@@ -8376,7 +8376,7 @@
         <v>Minor</v>
       </c>
       <c r="H90" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I90" t="str">
         <v>25/05/2026</v>
@@ -8447,13 +8447,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="str">
-        <v>EN60090</v>
+        <v>ENNE40</v>
       </c>
       <c r="C91" t="str">
-        <v>RF Site 31</v>
+        <v>RF Site 20</v>
       </c>
       <c r="D91" t="str">
-        <v>Sample Granite Relay (NEOA)</v>
+        <v>Sample Unity Switching (NEOA)</v>
       </c>
       <c r="E91" t="str">
         <v>Complete site</v>
@@ -8536,13 +8536,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="str">
-        <v>EN60091</v>
+        <v>ENNE41</v>
       </c>
       <c r="C92" t="str">
-        <v>RF Site 38</v>
+        <v>RF Site 11</v>
       </c>
       <c r="D92" t="str">
-        <v>Sample Northstar Switching (EOA)</v>
+        <v>Sample Lagoon Gateway (NEOA)</v>
       </c>
       <c r="E92" t="str">
         <v>IP Link Down</v>
@@ -8554,7 +8554,7 @@
         <v>Major</v>
       </c>
       <c r="H92" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I92" t="str">
         <v>04/05/2026</v>
@@ -8625,13 +8625,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="str">
-        <v>EN60092</v>
+        <v>ENNE42</v>
       </c>
       <c r="C93" t="str">
-        <v>RF Site 45</v>
+        <v>RF Site 12</v>
       </c>
       <c r="D93" t="str">
-        <v>Sample Unity Terminal (NEOA)</v>
+        <v>Sample Metro Hub (NEOA)</v>
       </c>
       <c r="E93" t="str">
         <v>Repeater</v>
@@ -8714,13 +8714,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="str">
-        <v>EN60093</v>
+        <v>ENNE43</v>
       </c>
       <c r="C94" t="str">
-        <v>RF Site 52</v>
+        <v>RF Site 13</v>
       </c>
       <c r="D94" t="str">
-        <v>Sample Cedar Node (EOA)</v>
+        <v>Sample Northstar Relay (NEOA)</v>
       </c>
       <c r="E94" t="str">
         <v>Router</v>
@@ -8732,7 +8732,7 @@
         <v>Critical</v>
       </c>
       <c r="H94" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I94" t="str">
         <v>10/05/2026</v>
@@ -8803,13 +8803,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="str">
-        <v>EN60094</v>
+        <v>ENNE44</v>
       </c>
       <c r="C95" t="str">
-        <v>RF Site 59</v>
+        <v>RF Site 14</v>
       </c>
       <c r="D95" t="str">
-        <v>Sample Jasmine Gateway (NEOA)</v>
+        <v>Sample Orchid Switching (NEOA)</v>
       </c>
       <c r="E95" t="str">
         <v>Switch</v>
@@ -8892,13 +8892,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="str">
-        <v>EN60095</v>
+        <v>ENNE45</v>
       </c>
       <c r="C96" t="str">
-        <v>RF Site 06</v>
+        <v>RF Site 15</v>
       </c>
       <c r="D96" t="str">
-        <v>Sample Granite Hub (EOA)</v>
+        <v>Sample Palm Terminal (NEOA)</v>
       </c>
       <c r="E96" t="str">
         <v>MW Link</v>
@@ -8910,7 +8910,7 @@
         <v>Minor</v>
       </c>
       <c r="H96" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I96" t="str">
         <v>16/05/2026</v>
@@ -8981,13 +8981,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="str">
-        <v>EN60096</v>
+        <v>ENNE46</v>
       </c>
       <c r="C97" t="str">
-        <v>RF Site 13</v>
+        <v>RF Site 16</v>
       </c>
       <c r="D97" t="str">
-        <v>Sample Northstar Relay (NEOA)</v>
+        <v>Sample Quartz Node (NEOA)</v>
       </c>
       <c r="E97" t="str">
         <v>Power System</v>
@@ -9070,13 +9070,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="str">
-        <v>EN60097</v>
+        <v>ENNE47</v>
       </c>
       <c r="C98" t="str">
-        <v>RF Site 20</v>
+        <v>RF Site 17</v>
       </c>
       <c r="D98" t="str">
-        <v>Sample Unity Switching (EOA)</v>
+        <v>Sample River Gateway (NEOA)</v>
       </c>
       <c r="E98" t="str">
         <v>Transmission Node</v>
@@ -9088,7 +9088,7 @@
         <v>Major</v>
       </c>
       <c r="H98" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I98" t="str">
         <v>22/05/2026</v>
@@ -9159,13 +9159,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="str">
-        <v>EN60098</v>
+        <v>ENNE48</v>
       </c>
       <c r="C99" t="str">
-        <v>RF Site 27</v>
+        <v>RF Site 18</v>
       </c>
       <c r="D99" t="str">
-        <v>Sample Cedar Terminal (NEOA)</v>
+        <v>Sample Summit Hub (NEOA)</v>
       </c>
       <c r="E99" t="str">
         <v>Access Node</v>
@@ -9248,13 +9248,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="str">
-        <v>EN60099</v>
+        <v>ENNE49</v>
       </c>
       <c r="C100" t="str">
-        <v>RF Site 34</v>
+        <v>RF Site 19</v>
       </c>
       <c r="D100" t="str">
-        <v>Sample Jasmine Node (EOA)</v>
+        <v>Sample Tide Relay (NEOA)</v>
       </c>
       <c r="E100" t="str">
         <v>Signal and Coverage issue</v>
@@ -9266,7 +9266,7 @@
         <v>Critical</v>
       </c>
       <c r="H100" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
       <c r="I100" t="str">
         <v>01/05/2026</v>
@@ -9337,13 +9337,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="str">
-        <v>EN60100</v>
+        <v>ENNE50</v>
       </c>
       <c r="C101" t="str">
-        <v>RF Site 41</v>
+        <v>RF Site 20</v>
       </c>
       <c r="D101" t="str">
-        <v>Sample Quartz Gateway (NEOA)</v>
+        <v>Sample Unity Switching (NEOA)</v>
       </c>
       <c r="E101" t="str">
         <v>Complete site</v>
@@ -9430,11 +9430,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D21"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="34.83203125" customWidth="1"/>
+    <col min="3" max="3" width="32.83203125" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9474,10 +9474,10 @@
         <v>RF Site 02</v>
       </c>
       <c r="C3" t="str">
-        <v>Sample Cedar Switching (NEOA)</v>
+        <v>Sample Cedar Switching (EOA)</v>
       </c>
       <c r="D3" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
     </row>
     <row r="4">
@@ -9502,10 +9502,10 @@
         <v>RF Site 04</v>
       </c>
       <c r="C5" t="str">
-        <v>Sample Emerald Node (NEOA)</v>
+        <v>Sample Emerald Node (EOA)</v>
       </c>
       <c r="D5" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
     </row>
     <row r="6">
@@ -9530,10 +9530,10 @@
         <v>RF Site 06</v>
       </c>
       <c r="C7" t="str">
-        <v>Sample Granite Hub (NEOA)</v>
+        <v>Sample Granite Hub (EOA)</v>
       </c>
       <c r="D7" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
     </row>
     <row r="8">
@@ -9558,10 +9558,10 @@
         <v>RF Site 08</v>
       </c>
       <c r="C9" t="str">
-        <v>Sample Ivory Switching (NEOA)</v>
+        <v>Sample Ivory Switching (EOA)</v>
       </c>
       <c r="D9" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
     </row>
     <row r="10">
@@ -9586,10 +9586,10 @@
         <v>RF Site 10</v>
       </c>
       <c r="C11" t="str">
-        <v>Sample Kingfisher Node (NEOA)</v>
+        <v>Sample Kingfisher Node (EOA)</v>
       </c>
       <c r="D11" t="str">
-        <v>NEOA</v>
+        <v>EOA</v>
       </c>
     </row>
     <row r="12">
@@ -9600,10 +9600,10 @@
         <v>RF Site 11</v>
       </c>
       <c r="C12" t="str">
-        <v>Sample Lagoon Gateway (EOA)</v>
+        <v>Sample Lagoon Gateway (NEOA)</v>
       </c>
       <c r="D12" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
     </row>
     <row r="13">
@@ -9628,10 +9628,10 @@
         <v>RF Site 13</v>
       </c>
       <c r="C14" t="str">
-        <v>Sample Northstar Relay (EOA)</v>
+        <v>Sample Northstar Relay (NEOA)</v>
       </c>
       <c r="D14" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
     </row>
     <row r="15">
@@ -9656,10 +9656,10 @@
         <v>RF Site 15</v>
       </c>
       <c r="C16" t="str">
-        <v>Sample Palm Terminal (EOA)</v>
+        <v>Sample Palm Terminal (NEOA)</v>
       </c>
       <c r="D16" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
     </row>
     <row r="17">
@@ -9684,10 +9684,10 @@
         <v>RF Site 17</v>
       </c>
       <c r="C18" t="str">
-        <v>Sample River Gateway (EOA)</v>
+        <v>Sample River Gateway (NEOA)</v>
       </c>
       <c r="D18" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
     </row>
     <row r="19">
@@ -9712,10 +9712,10 @@
         <v>RF Site 19</v>
       </c>
       <c r="C20" t="str">
-        <v>Sample Tide Relay (EOA)</v>
+        <v>Sample Tide Relay (NEOA)</v>
       </c>
       <c r="D20" t="str">
-        <v>EOA</v>
+        <v>NEOA</v>
       </c>
     </row>
     <row r="21">
@@ -9732,569 +9732,9 @@
         <v>NEOA</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="str">
-        <v>RF Site 21</v>
-      </c>
-      <c r="C22" t="str">
-        <v>Sample Vertex Terminal (EOA)</v>
-      </c>
-      <c r="D22" t="str">
-        <v>EOA</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="str">
-        <v>RF Site 22</v>
-      </c>
-      <c r="C23" t="str">
-        <v>Sample Westbay Node (NEOA)</v>
-      </c>
-      <c r="D23" t="str">
-        <v>NEOA</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="str">
-        <v>RF Site 23</v>
-      </c>
-      <c r="C24" t="str">
-        <v>Sample Yard Gateway (EOA)</v>
-      </c>
-      <c r="D24" t="str">
-        <v>EOA</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="str">
-        <v>RF Site 24</v>
-      </c>
-      <c r="C25" t="str">
-        <v>Sample Zenith Hub (NEOA)</v>
-      </c>
-      <c r="D25" t="str">
-        <v>NEOA</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="str">
-        <v>RF Site 25</v>
-      </c>
-      <c r="C26" t="str">
-        <v>Sample Alpha Relay (EOA)</v>
-      </c>
-      <c r="D26" t="str">
-        <v>EOA</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="str">
-        <v>RF Site 26</v>
-      </c>
-      <c r="C27" t="str">
-        <v>Sample Bravo Switching (NEOA)</v>
-      </c>
-      <c r="D27" t="str">
-        <v>NEOA</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="str">
-        <v>RF Site 27</v>
-      </c>
-      <c r="C28" t="str">
-        <v>Sample Cedar Terminal (EOA)</v>
-      </c>
-      <c r="D28" t="str">
-        <v>EOA</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="str">
-        <v>RF Site 28</v>
-      </c>
-      <c r="C29" t="str">
-        <v>Sample Delta Node (NEOA)</v>
-      </c>
-      <c r="D29" t="str">
-        <v>NEOA</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="str">
-        <v>RF Site 29</v>
-      </c>
-      <c r="C30" t="str">
-        <v>Sample Emerald Gateway (EOA)</v>
-      </c>
-      <c r="D30" t="str">
-        <v>EOA</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="str">
-        <v>RF Site 30</v>
-      </c>
-      <c r="C31" t="str">
-        <v>Sample Falcon Hub (NEOA)</v>
-      </c>
-      <c r="D31" t="str">
-        <v>NEOA</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="str">
-        <v>RF Site 31</v>
-      </c>
-      <c r="C32" t="str">
-        <v>Sample Granite Relay (EOA)</v>
-      </c>
-      <c r="D32" t="str">
-        <v>EOA</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="str">
-        <v>RF Site 32</v>
-      </c>
-      <c r="C33" t="str">
-        <v>Sample Harbor Switching (NEOA)</v>
-      </c>
-      <c r="D33" t="str">
-        <v>NEOA</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="str">
-        <v>RF Site 33</v>
-      </c>
-      <c r="C34" t="str">
-        <v>Sample Ivory Terminal (EOA)</v>
-      </c>
-      <c r="D34" t="str">
-        <v>EOA</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="str">
-        <v>RF Site 34</v>
-      </c>
-      <c r="C35" t="str">
-        <v>Sample Jasmine Node (NEOA)</v>
-      </c>
-      <c r="D35" t="str">
-        <v>NEOA</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="str">
-        <v>RF Site 35</v>
-      </c>
-      <c r="C36" t="str">
-        <v>Sample Kingfisher Gateway (EOA)</v>
-      </c>
-      <c r="D36" t="str">
-        <v>EOA</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="str">
-        <v>RF Site 36</v>
-      </c>
-      <c r="C37" t="str">
-        <v>Sample Lagoon Hub (NEOA)</v>
-      </c>
-      <c r="D37" t="str">
-        <v>NEOA</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="str">
-        <v>RF Site 37</v>
-      </c>
-      <c r="C38" t="str">
-        <v>Sample Metro Relay (EOA)</v>
-      </c>
-      <c r="D38" t="str">
-        <v>EOA</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="str">
-        <v>RF Site 38</v>
-      </c>
-      <c r="C39" t="str">
-        <v>Sample Northstar Switching (NEOA)</v>
-      </c>
-      <c r="D39" t="str">
-        <v>NEOA</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="str">
-        <v>RF Site 39</v>
-      </c>
-      <c r="C40" t="str">
-        <v>Sample Orchid Terminal (EOA)</v>
-      </c>
-      <c r="D40" t="str">
-        <v>EOA</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="str">
-        <v>RF Site 40</v>
-      </c>
-      <c r="C41" t="str">
-        <v>Sample Palm Node (NEOA)</v>
-      </c>
-      <c r="D41" t="str">
-        <v>NEOA</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="str">
-        <v>RF Site 41</v>
-      </c>
-      <c r="C42" t="str">
-        <v>Sample Quartz Gateway (EOA)</v>
-      </c>
-      <c r="D42" t="str">
-        <v>EOA</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="str">
-        <v>RF Site 42</v>
-      </c>
-      <c r="C43" t="str">
-        <v>Sample River Hub (NEOA)</v>
-      </c>
-      <c r="D43" t="str">
-        <v>NEOA</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="str">
-        <v>RF Site 43</v>
-      </c>
-      <c r="C44" t="str">
-        <v>Sample Summit Relay (EOA)</v>
-      </c>
-      <c r="D44" t="str">
-        <v>EOA</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="str">
-        <v>RF Site 44</v>
-      </c>
-      <c r="C45" t="str">
-        <v>Sample Tide Switching (NEOA)</v>
-      </c>
-      <c r="D45" t="str">
-        <v>NEOA</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
-        <v>RF Site 45</v>
-      </c>
-      <c r="C46" t="str">
-        <v>Sample Unity Terminal (EOA)</v>
-      </c>
-      <c r="D46" t="str">
-        <v>EOA</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>RF Site 46</v>
-      </c>
-      <c r="C47" t="str">
-        <v>Sample Vertex Node (NEOA)</v>
-      </c>
-      <c r="D47" t="str">
-        <v>NEOA</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>RF Site 47</v>
-      </c>
-      <c r="C48" t="str">
-        <v>Sample Westbay Gateway (EOA)</v>
-      </c>
-      <c r="D48" t="str">
-        <v>EOA</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>RF Site 48</v>
-      </c>
-      <c r="C49" t="str">
-        <v>Sample Yard Hub (NEOA)</v>
-      </c>
-      <c r="D49" t="str">
-        <v>NEOA</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>RF Site 49</v>
-      </c>
-      <c r="C50" t="str">
-        <v>Sample Zenith Relay (EOA)</v>
-      </c>
-      <c r="D50" t="str">
-        <v>EOA</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>RF Site 50</v>
-      </c>
-      <c r="C51" t="str">
-        <v>Sample Alpha Switching (NEOA)</v>
-      </c>
-      <c r="D51" t="str">
-        <v>NEOA</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>RF Site 51</v>
-      </c>
-      <c r="C52" t="str">
-        <v>Sample Bravo Terminal (EOA)</v>
-      </c>
-      <c r="D52" t="str">
-        <v>EOA</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>RF Site 52</v>
-      </c>
-      <c r="C53" t="str">
-        <v>Sample Cedar Node (NEOA)</v>
-      </c>
-      <c r="D53" t="str">
-        <v>NEOA</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>RF Site 53</v>
-      </c>
-      <c r="C54" t="str">
-        <v>Sample Delta Gateway (EOA)</v>
-      </c>
-      <c r="D54" t="str">
-        <v>EOA</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>RF Site 54</v>
-      </c>
-      <c r="C55" t="str">
-        <v>Sample Emerald Hub (NEOA)</v>
-      </c>
-      <c r="D55" t="str">
-        <v>NEOA</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>RF Site 55</v>
-      </c>
-      <c r="C56" t="str">
-        <v>Sample Falcon Relay (EOA)</v>
-      </c>
-      <c r="D56" t="str">
-        <v>EOA</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>RF Site 56</v>
-      </c>
-      <c r="C57" t="str">
-        <v>Sample Granite Switching (NEOA)</v>
-      </c>
-      <c r="D57" t="str">
-        <v>NEOA</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>RF Site 57</v>
-      </c>
-      <c r="C58" t="str">
-        <v>Sample Harbor Terminal (EOA)</v>
-      </c>
-      <c r="D58" t="str">
-        <v>EOA</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>RF Site 58</v>
-      </c>
-      <c r="C59" t="str">
-        <v>Sample Ivory Node (NEOA)</v>
-      </c>
-      <c r="D59" t="str">
-        <v>NEOA</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>RF Site 59</v>
-      </c>
-      <c r="C60" t="str">
-        <v>Sample Jasmine Gateway (EOA)</v>
-      </c>
-      <c r="D60" t="str">
-        <v>EOA</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>RF Site 60</v>
-      </c>
-      <c r="C61" t="str">
-        <v>Sample Kingfisher Hub (NEOA)</v>
-      </c>
-      <c r="D61" t="str">
-        <v>NEOA</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D21"/>
   </ignoredErrors>
 </worksheet>
 </file>
